--- a/data/trans_dic/IP16A01-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/IP16A01-Provincia-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -526,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que consumiero medicamentos para  el catarro, gripe, garganta, bronquios</t>
+          <t>Menores que consumiero medicamentos para  el catarro, gripe, garganta, bronquios (tasa de respuesta: 99,94%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -638,7 +639,7 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>Almeria</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -716,69 +717,69 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>90,51; 100</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>66,41; 93,52</t>
+          <t>64,57; 93,58</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>28,27; 70,37</t>
+          <t>27,14; 69,46</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>19,43; 59,37</t>
+          <t>19,54; 56,95</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>89,47; 100</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>34,05; 72,04</t>
+          <t>33,18; 72,58</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>41,21; 76,37</t>
+          <t>37,92; 77,2</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>37,05; 73,15</t>
+          <t>39,08; 73,18</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>94,84; 100</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>51,25; 78,8</t>
+          <t>52,76; 79,74</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>40,69; 69,17</t>
+          <t>40,39; 68,26</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>29,33; 59,07</t>
+          <t>30,81; 59,63</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>Cadiz</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -856,69 +857,69 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>93,19; 100</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>41,98; 73,99</t>
+          <t>41,44; 73,72</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>56,45; 87,36</t>
+          <t>58,18; 85,8</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>36,75; 89,2</t>
+          <t>37,89; 90,45</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>93,85; 100</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>44,4; 75,38</t>
+          <t>44,91; 76,31</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>32,47; 68,17</t>
+          <t>33,6; 67,37</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>43,05; 67,98</t>
+          <t>42,88; 67,66</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>96,7; 100</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>47,93; 70,99</t>
+          <t>48,36; 70,62</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>53,04; 74,2</t>
+          <t>52,24; 75,04</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>47,1; 81,69</t>
+          <t>46,95; 82,83</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>Cordoba</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -996,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>88,85; 100</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>47,11; 89,62</t>
+          <t>46,99; 86,47</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>23,16; 76,42</t>
+          <t>23,14; 77,28</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>54,24; 86,83</t>
+          <t>52,19; 86,22</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>89,47; 100</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>62,97; 93,17</t>
+          <t>62,25; 91,31</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>31,27; 82,92</t>
+          <t>31,59; 83,07</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>51,94; 86,3</t>
+          <t>54,57; 89,07</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>94,39; 100</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>63,1; 86,26</t>
+          <t>63,47; 87,01</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>35,26; 75,35</t>
+          <t>34,53; 74,97</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>59,41; 82,65</t>
+          <t>59,03; 82,32</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>92,39; 100</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>62,3; 91,4</t>
+          <t>62,03; 93,57</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>38,05; 71,08</t>
+          <t>38,71; 71,03</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>27,26; 77,23</t>
+          <t>26,05; 74,1</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>92,07; 100</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>44,04; 82,65</t>
+          <t>44,71; 84,9</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>43,36; 76,34</t>
+          <t>41,9; 74,71</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>40,17; 91,69</t>
+          <t>37,49; 92,26</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>96,02; 100</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>60,02; 85,0</t>
+          <t>61,84; 85,46</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>46,82; 68,63</t>
+          <t>45,05; 69,35</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>39,47; 78,11</t>
+          <t>40,97; 77,72</t>
         </is>
       </c>
     </row>
@@ -1276,69 +1277,69 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>86,51; 100</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>58,45; 95,42</t>
+          <t>59,39; 95,47</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>52,6; 100,0</t>
+          <t>52,26; 100,0</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>44,01; 88,21</t>
+          <t>44,67; 89,58</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>84,31; 100</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>55,26; 94,76</t>
+          <t>54,98; 94,67</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>32,67; 100,0</t>
+          <t>31,67; 100,0</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>17,37; 69,16</t>
+          <t>19,46; 69,84</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>92,39; 100</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>66,14; 91,83</t>
+          <t>65,44; 91,53</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>56,17; 95,01</t>
+          <t>53,92; 94,7</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>34,31; 73,0</t>
+          <t>35,16; 74,36</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>Jaen</t>
+          <t>Jaén</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1416,69 +1417,69 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>90,01; 100</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>30,1; 81,45</t>
+          <t>30,05; 78,9</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>23,37; 79,29</t>
+          <t>29,41; 84,36</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>29,93; 84,2</t>
+          <t>30,69; 86,15</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>89,47; 100</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>36,6; 75,22</t>
+          <t>36,51; 75,63</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>9,17; 68,79</t>
+          <t>9,36; 70,21</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>53,36; 91,26</t>
+          <t>53,35; 89,97</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>94,7; 100</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>41,53; 71,93</t>
+          <t>41,33; 71,96</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>27,99; 65,1</t>
+          <t>25,89; 66,32</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>53,29; 82,99</t>
+          <t>53,75; 84,16</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>Malaga</t>
+          <t>Málaga</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -1556,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>94,04; 100</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>44,19; 74,97</t>
+          <t>45,19; 76,22</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>43,21; 85,1</t>
+          <t>44,27; 84,81</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>35,91; 66,86</t>
+          <t>36,22; 67,08</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>95,1; 100</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>39,27; 71,2</t>
+          <t>40,33; 71,29</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>49,38; 93,68</t>
+          <t>44,24; 93,81</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>35,9; 67,88</t>
+          <t>36,73; 69,92</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>97,26; 100</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>47,7; 70,75</t>
+          <t>46,23; 69,52</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>54,49; 83,87</t>
+          <t>55,6; 84,25</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>40,4; 63,73</t>
+          <t>40,91; 63,63</t>
         </is>
       </c>
     </row>
@@ -1696,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>95,56; 100</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>35,27; 69,34</t>
+          <t>35,45; 68,92</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>36,02; 71,73</t>
+          <t>39,56; 72,04</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>35,05; 88,08</t>
+          <t>33,66; 87,15</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>96,96; 100</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>35,64; 71,15</t>
+          <t>37,1; 72,18</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>27,59; 57,54</t>
+          <t>28,17; 60,27</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>35,15; 83,63</t>
+          <t>31,23; 83,43</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>98,17; 100</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>41,21; 65,16</t>
+          <t>39,2; 64,84</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>37,62; 60,87</t>
+          <t>36,91; 59,23</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>41,83; 78,62</t>
+          <t>42,9; 79,78</t>
         </is>
       </c>
     </row>
@@ -1836,62 +1837,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>99,0; 100</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>60,7; 73,37</t>
+          <t>60,42; 72,9</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>53,45; 68,0</t>
+          <t>54,28; 68,45</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>48,7; 76,03</t>
+          <t>47,96; 74,88</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>99,11; 100</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>55,88; 68,32</t>
+          <t>56,39; 68,87</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>47,55; 62,83</t>
+          <t>47,95; 62,67</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>53,0; 66,52</t>
+          <t>51,99; 65,84</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>99,53; 100</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>60,41; 69,13</t>
+          <t>60,25; 69,2</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>53,08; 63,13</t>
+          <t>53,5; 63,19</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>52,86; 68,42</t>
+          <t>52,52; 67,87</t>
         </is>
       </c>
     </row>
@@ -1920,4 +1921,2040 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:N31"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Menores que consumiero medicamentos para  el catarro, gripe, garganta, bronquios (tasa de respuesta: 99,94%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="n"/>
+      <c r="E1" s="3" t="n"/>
+      <c r="F1" s="3" t="n"/>
+      <c r="G1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="H1" s="3" t="n"/>
+      <c r="I1" s="3" t="n"/>
+      <c r="J1" s="3" t="n"/>
+      <c r="K1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="L1" s="3" t="n"/>
+      <c r="M1" s="3" t="n"/>
+      <c r="N1" s="3" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="L2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="M2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="N2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
+      <c r="J3" s="2" t="n"/>
+      <c r="K3" s="2" t="n"/>
+      <c r="L3" s="2" t="n"/>
+      <c r="M3" s="2" t="n"/>
+      <c r="N3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>Almería</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>11668</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>13339</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>7811</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>11595</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>12135</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>9861</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>11564</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>12469</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>23803</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>23200</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>19375</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>24063</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>10391; 15059</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>4368; 11178</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>5937; 17304</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>6182; 13521</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>7283; 14827</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>8723; 16335</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>18322; 27688</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>14258; 24093</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>16238; 31430</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>Cádiz</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>66</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>16730</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>13893</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>20181</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>42319</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>19856</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>15016</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>10658</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>26760</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>36586</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>28909</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>30839</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>69079</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>9730; 17312</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>15861; 23392</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>23890; 57034</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>11217; 19058</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>6948; 13934</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>20653; 32587</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>23434; 34222</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>25046; 35979</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>52221; 92122</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>Córdoba</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>11627</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>10347</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>5020</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>12943</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>10561</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>17759</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>4802</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>14671</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>22188</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>28107</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>9822</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>27614</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>6873; 12648</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>2204; 7359</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>9363; 15468</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>13887; 20371</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>2635; 6928</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>11071; 18069</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>23442; 32136</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>6167; 13392</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>22567; 31469</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Granada</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>16351</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>15523</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>13092</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>6258</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>16426</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>10184</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>15273</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>7973</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>32777</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>25708</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>28364</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>14230</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>11983; 18076</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>9214; 16904</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>3262; 9278</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>6815; 12941</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>10719; 19111</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>4151; 10216</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>21373; 29536</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>22248; 34243</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>9665; 18336</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Huelva</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>9126</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>12223</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>5740</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>5810</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>7820</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>9660</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>3757</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>4570</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>16947</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>21883</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>9497</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>10381</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>8616; 13850</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>3403; 6511</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>3680; 7379</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>6755; 11633</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>1637; 5168</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>2081; 7465</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>17534; 24525</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>6297; 11060</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>6654; 14073</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>Jaén</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="n"/>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>12379</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>6141</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>5031</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>4639</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>10729</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>10346</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>3167</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>10347</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>23108</t>
+        </is>
+      </c>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>16487</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>8198</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t>14987</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="n"/>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>3302; 8670</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>2678; 7681</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>2357; 6616</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>6605; 13683</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>813; 6097</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
+          <t>7260; 12242</t>
+        </is>
+      </c>
+      <c r="K21" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>12018; 20927</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr">
+        <is>
+          <t>4606; 11799</t>
+        </is>
+      </c>
+      <c r="N21" s="2" t="inlineStr">
+        <is>
+          <t>11441; 17916</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>Málaga</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>69</t>
+        </is>
+      </c>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t>54</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="n"/>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>21499</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>16099</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>9539</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>15347</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>26526</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>14259</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>7947</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>23789</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>48025</t>
+        </is>
+      </c>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>30358</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>17486</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr">
+        <is>
+          <t>39136</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="n"/>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>12003; 20244</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>6308; 12085</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>10790; 19981</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>10221; 18069</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>4691; 9947</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>16292; 31013</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>23996; 36086</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>13820; 20940</t>
+        </is>
+      </c>
+      <c r="N24" s="2" t="inlineStr">
+        <is>
+          <t>30334; 47173</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="inlineStr">
+        <is>
+          <t>Sevilla</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="K25" s="2" t="inlineStr">
+        <is>
+          <t>104</t>
+        </is>
+      </c>
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="N25" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="n"/>
+      <c r="B26" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>25924</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>11121</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>11800</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>5106</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>39867</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>11862</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>10811</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t>6982</t>
+        </is>
+      </c>
+      <c r="K26" s="2" t="inlineStr">
+        <is>
+          <t>65790</t>
+        </is>
+      </c>
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t>22983</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr">
+        <is>
+          <t>22610</t>
+        </is>
+      </c>
+      <c r="N26" s="2" t="inlineStr">
+        <is>
+          <t>12088</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="n"/>
+      <c r="B27" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>7524; 14626</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>8275; 15070</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>2730; 7071</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>8048; 15658</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>7047; 15074</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
+          <t>3656; 9767</t>
+        </is>
+      </c>
+      <c r="K27" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="L27" s="2" t="inlineStr">
+        <is>
+          <t>16822; 27826</t>
+        </is>
+      </c>
+      <c r="M27" s="2" t="inlineStr">
+        <is>
+          <t>16953; 27203</t>
+        </is>
+      </c>
+      <c r="N27" s="2" t="inlineStr">
+        <is>
+          <t>8502; 15811</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>190</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>141</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>119</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>125</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>215</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>138</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
+          <t>155</t>
+        </is>
+      </c>
+      <c r="K28" s="2" t="inlineStr">
+        <is>
+          <t>405</t>
+        </is>
+      </c>
+      <c r="L28" s="2" t="inlineStr">
+        <is>
+          <t>279</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="inlineStr">
+        <is>
+          <t>219</t>
+        </is>
+      </c>
+      <c r="N28" s="2" t="inlineStr">
+        <is>
+          <t>280</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="n"/>
+      <c r="B29" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>125305</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>98686</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>78212</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>104018</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>143919</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>98947</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>67979</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
+          <t>107562</t>
+        </is>
+      </c>
+      <c r="K29" s="2" t="inlineStr">
+        <is>
+          <t>269224</t>
+        </is>
+      </c>
+      <c r="L29" s="2" t="inlineStr">
+        <is>
+          <t>197633</t>
+        </is>
+      </c>
+      <c r="M29" s="2" t="inlineStr">
+        <is>
+          <t>146191</t>
+        </is>
+      </c>
+      <c r="N29" s="2" t="inlineStr">
+        <is>
+          <t>211579</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="n"/>
+      <c r="B30" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>88690; 107012</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>69181; 87247</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>85233; 133075</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>89414; 109213</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>59106; 77262</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
+          <t>94726; 119965</t>
+        </is>
+      </c>
+      <c r="K30" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="L30" s="2" t="inlineStr">
+        <is>
+          <t>183996; 211302</t>
+        </is>
+      </c>
+      <c r="M30" s="2" t="inlineStr">
+        <is>
+          <t>134154; 158441</t>
+        </is>
+      </c>
+      <c r="N30" s="2" t="inlineStr">
+        <is>
+          <t>189045; 244269</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="13">
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="A25:A27"/>
+    <mergeCell ref="A28:A30"/>
+    <mergeCell ref="A19:A21"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="C1:F1"/>
+    <mergeCell ref="G1:J1"/>
+    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="A22:A24"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/IP16A01-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/IP16A01-Provincia-trans_dic.xlsx
@@ -722,17 +722,17 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>64,57; 93,58</t>
+          <t>64,37; 93,88</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>27,14; 69,46</t>
+          <t>27,34; 68,53</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>19,54; 56,95</t>
+          <t>17,77; 56,08</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -742,17 +742,17 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>33,18; 72,58</t>
+          <t>33,46; 73,11</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>37,92; 77,2</t>
+          <t>41,04; 77,6</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>39,08; 73,18</t>
+          <t>36,11; 74,03</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -762,17 +762,17 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>52,76; 79,74</t>
+          <t>52,54; 79,42</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>40,39; 68,26</t>
+          <t>41,19; 67,54</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>30,81; 59,63</t>
+          <t>27,71; 59,57</t>
         </is>
       </c>
     </row>
@@ -862,17 +862,17 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>41,44; 73,72</t>
+          <t>42,48; 75,63</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>58,18; 85,8</t>
+          <t>56,81; 85,38</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>37,89; 90,45</t>
+          <t>36,66; 89,47</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -882,17 +882,17 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>44,91; 76,31</t>
+          <t>43,33; 76,14</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>33,6; 67,37</t>
+          <t>31,14; 67,39</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>42,88; 67,66</t>
+          <t>42,82; 68,04</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -902,17 +902,17 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>48,36; 70,62</t>
+          <t>47,88; 69,26</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>52,24; 75,04</t>
+          <t>53,15; 76,14</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>46,95; 82,83</t>
+          <t>47,28; 81,69</t>
         </is>
       </c>
     </row>
@@ -1002,17 +1002,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>46,99; 86,47</t>
+          <t>49,84; 89,72</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>23,14; 77,28</t>
+          <t>23,02; 76,42</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>52,19; 86,22</t>
+          <t>53,25; 87,1</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1022,17 +1022,17 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>62,25; 91,31</t>
+          <t>59,82; 90,51</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>31,59; 83,07</t>
+          <t>31,83; 83,21</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>54,57; 89,07</t>
+          <t>54,43; 87,08</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
@@ -1042,17 +1042,17 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>63,47; 87,01</t>
+          <t>63,82; 86,51</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>34,53; 74,97</t>
+          <t>34,08; 74,94</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>59,03; 82,32</t>
+          <t>59,16; 83,99</t>
         </is>
       </c>
     </row>
@@ -1142,17 +1142,17 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>62,03; 93,57</t>
+          <t>62,1; 92,74</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>38,71; 71,03</t>
+          <t>37,93; 71,26</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>26,05; 74,1</t>
+          <t>26,27; 77,17</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1162,17 +1162,17 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>44,71; 84,9</t>
+          <t>43,65; 84,12</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>41,9; 74,71</t>
+          <t>42,24; 74,66</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>37,49; 92,26</t>
+          <t>40,51; 91,61</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -1182,17 +1182,17 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>61,84; 85,46</t>
+          <t>61,03; 84,68</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>45,05; 69,35</t>
+          <t>46,03; 68,61</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>40,97; 77,72</t>
+          <t>41,34; 77,71</t>
         </is>
       </c>
     </row>
@@ -1282,17 +1282,17 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>59,39; 95,47</t>
+          <t>62,28; 95,54</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>52,26; 100,0</t>
+          <t>50,97; 100,0</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>44,67; 89,58</t>
+          <t>42,99; 89,06</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1302,17 +1302,17 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>54,98; 94,67</t>
+          <t>54,39; 94,74</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>31,67; 100,0</t>
+          <t>32,38; 100,0</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>19,46; 69,84</t>
+          <t>20,06; 71,27</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -1322,17 +1322,17 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>65,44; 91,53</t>
+          <t>66,37; 91,84</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>53,92; 94,7</t>
+          <t>53,67; 94,6</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>35,16; 74,36</t>
+          <t>33,53; 74,66</t>
         </is>
       </c>
     </row>
@@ -1422,17 +1422,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>30,05; 78,9</t>
+          <t>31,28; 81,34</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>29,41; 84,36</t>
+          <t>29,59; 83,93</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>30,69; 86,15</t>
+          <t>30,44; 84,33</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1442,17 +1442,17 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>36,51; 75,63</t>
+          <t>36,89; 75,49</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>9,36; 70,21</t>
+          <t>15,23; 72,44</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>53,35; 89,97</t>
+          <t>53,46; 89,93</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
@@ -1462,17 +1462,17 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>41,33; 71,96</t>
+          <t>42,65; 71,67</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>25,89; 66,32</t>
+          <t>26,25; 67,08</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>53,75; 84,16</t>
+          <t>53,75; 84,13</t>
         </is>
       </c>
     </row>
@@ -1562,17 +1562,17 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>45,19; 76,22</t>
+          <t>44,21; 75,0</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>44,27; 84,81</t>
+          <t>44,43; 85,55</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>36,22; 67,08</t>
+          <t>36,89; 66,43</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -1582,17 +1582,17 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>40,33; 71,29</t>
+          <t>39,96; 71,74</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>44,24; 93,81</t>
+          <t>48,58; 93,42</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>36,73; 69,92</t>
+          <t>37,52; 68,27</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -1602,17 +1602,17 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>46,23; 69,52</t>
+          <t>46,63; 69,0</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>55,6; 84,25</t>
+          <t>53,62; 83,72</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>40,91; 63,63</t>
+          <t>40,06; 63,18</t>
         </is>
       </c>
     </row>
@@ -1702,17 +1702,17 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>35,45; 68,92</t>
+          <t>34,15; 71,3</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>39,56; 72,04</t>
+          <t>36,9; 71,64</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>33,66; 87,15</t>
+          <t>33,84; 87,34</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -1722,17 +1722,17 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>37,1; 72,18</t>
+          <t>35,14; 71,3</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>28,17; 60,27</t>
+          <t>28,67; 59,74</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>31,23; 83,43</t>
+          <t>34,02; 85,27</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
@@ -1742,17 +1742,17 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>39,2; 64,84</t>
+          <t>40,88; 66,35</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>36,91; 59,23</t>
+          <t>37,47; 60,6</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>42,9; 79,78</t>
+          <t>40,94; 77,32</t>
         </is>
       </c>
     </row>
@@ -1842,17 +1842,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>60,42; 72,9</t>
+          <t>61,17; 73,9</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>54,28; 68,45</t>
+          <t>53,74; 68,17</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>47,96; 74,88</t>
+          <t>48,28; 74,25</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -1862,17 +1862,17 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>56,39; 68,87</t>
+          <t>56,07; 69,1</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>47,95; 62,67</t>
+          <t>47,78; 62,35</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>51,99; 65,84</t>
+          <t>52,18; 65,89</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
@@ -1882,17 +1882,17 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>60,25; 69,2</t>
+          <t>59,66; 69,02</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>53,5; 63,19</t>
+          <t>52,85; 62,89</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>52,52; 67,87</t>
+          <t>53,2; 67,73</t>
         </is>
       </c>
     </row>
@@ -2214,17 +2214,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>10391; 15059</t>
+          <t>10359; 15106</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>4368; 11178</t>
+          <t>4400; 11028</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>5937; 17304</t>
+          <t>5398; 17040</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -2234,17 +2234,17 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>6182; 13521</t>
+          <t>6234; 13622</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>7283; 14827</t>
+          <t>7882; 14903</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>8723; 16335</t>
+          <t>8060; 16525</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -2254,17 +2254,17 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>18322; 27688</t>
+          <t>18245; 27578</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>14258; 24093</t>
+          <t>14539; 23839</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>16238; 31430</t>
+          <t>14604; 31395</t>
         </is>
       </c>
     </row>
@@ -2422,17 +2422,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>9730; 17312</t>
+          <t>9976; 17759</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>15861; 23392</t>
+          <t>15489; 23277</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>23890; 57034</t>
+          <t>23113; 56416</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -2442,17 +2442,17 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>11217; 19058</t>
+          <t>10823; 19018</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>6948; 13934</t>
+          <t>6441; 13937</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>20653; 32587</t>
+          <t>20625; 32768</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
@@ -2462,17 +2462,17 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>23434; 34222</t>
+          <t>23203; 33563</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>25046; 35979</t>
+          <t>25483; 36505</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>52221; 92122</t>
+          <t>52583; 90851</t>
         </is>
       </c>
     </row>
@@ -2630,17 +2630,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>6873; 12648</t>
+          <t>7290; 13123</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>2204; 7359</t>
+          <t>2192; 7277</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>9363; 15468</t>
+          <t>9554; 15627</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -2650,17 +2650,17 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>13887; 20371</t>
+          <t>13345; 20192</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>2635; 6928</t>
+          <t>2654; 6939</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>11071; 18069</t>
+          <t>11042; 17666</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -2670,17 +2670,17 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>23442; 32136</t>
+          <t>23574; 31954</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>6167; 13392</t>
+          <t>6088; 13386</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>22567; 31469</t>
+          <t>22614; 32106</t>
         </is>
       </c>
     </row>
@@ -2838,17 +2838,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>11983; 18076</t>
+          <t>11997; 17916</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>9214; 16904</t>
+          <t>9028; 16960</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>3262; 9278</t>
+          <t>3289; 9663</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2858,17 +2858,17 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>6815; 12941</t>
+          <t>6653; 12822</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>10719; 19111</t>
+          <t>10805; 19098</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>4151; 10216</t>
+          <t>4486; 10144</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
@@ -2878,17 +2878,17 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>21373; 29536</t>
+          <t>21093; 29268</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>22248; 34243</t>
+          <t>22730; 33880</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>9665; 18336</t>
+          <t>9754; 18335</t>
         </is>
       </c>
     </row>
@@ -3046,17 +3046,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>8616; 13850</t>
+          <t>9035; 13861</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>3403; 6511</t>
+          <t>3319; 6511</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>3680; 7379</t>
+          <t>3541; 7336</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -3066,17 +3066,17 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>6755; 11633</t>
+          <t>6683; 11641</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>1637; 5168</t>
+          <t>1673; 5168</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>2081; 7465</t>
+          <t>2144; 7618</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -3086,17 +3086,17 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>17534; 24525</t>
+          <t>17783; 24609</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>6297; 11060</t>
+          <t>6268; 11048</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>6654; 14073</t>
+          <t>6347; 14130</t>
         </is>
       </c>
     </row>
@@ -3254,17 +3254,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>3302; 8670</t>
+          <t>3437; 8938</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>2678; 7681</t>
+          <t>2694; 7642</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>2357; 6616</t>
+          <t>2338; 6476</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -3274,17 +3274,17 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>6605; 13683</t>
+          <t>6674; 13658</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>813; 6097</t>
+          <t>1323; 6291</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>7260; 12242</t>
+          <t>7275; 12237</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
@@ -3294,17 +3294,17 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>12018; 20927</t>
+          <t>12404; 20841</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>4606; 11799</t>
+          <t>4670; 11933</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>11441; 17916</t>
+          <t>11442; 17908</t>
         </is>
       </c>
     </row>
@@ -3462,17 +3462,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>12003; 20244</t>
+          <t>11741; 19918</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>6308; 12085</t>
+          <t>6331; 12191</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>10790; 19981</t>
+          <t>10988; 19786</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3482,17 +3482,17 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>10221; 18069</t>
+          <t>10128; 18183</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>4691; 9947</t>
+          <t>5152; 9906</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>16292; 31013</t>
+          <t>16640; 30282</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
@@ -3502,17 +3502,17 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>23996; 36086</t>
+          <t>24201; 35814</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>13820; 20940</t>
+          <t>13326; 20807</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>30334; 47173</t>
+          <t>29701; 46845</t>
         </is>
       </c>
     </row>
@@ -3670,17 +3670,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>7524; 14626</t>
+          <t>7248; 15133</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>8275; 15070</t>
+          <t>7718; 14986</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>2730; 7071</t>
+          <t>2745; 7086</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3690,17 +3690,17 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>8048; 15658</t>
+          <t>7622; 15467</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>7047; 15074</t>
+          <t>7172; 14942</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>3656; 9767</t>
+          <t>3983; 9983</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
@@ -3710,17 +3710,17 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>16822; 27826</t>
+          <t>17545; 28472</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>16953; 27203</t>
+          <t>17211; 27833</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>8502; 15811</t>
+          <t>8115; 15324</t>
         </is>
       </c>
     </row>
@@ -3878,17 +3878,17 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>88690; 107012</t>
+          <t>89801; 108483</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>69181; 87247</t>
+          <t>68501; 86885</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>85233; 133075</t>
+          <t>85806; 131950</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3898,17 +3898,17 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>89414; 109213</t>
+          <t>88910; 109578</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>59106; 77262</t>
+          <t>58903; 76857</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>94726; 119965</t>
+          <t>95069; 120047</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
@@ -3918,17 +3918,17 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>183996; 211302</t>
+          <t>182190; 210777</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>134154; 158441</t>
+          <t>132523; 157678</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>189045; 244269</t>
+          <t>191488; 243782</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP16A01-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/IP16A01-Provincia-trans_dic.xlsx
@@ -527,13 +527,13 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que consumiero medicamentos para  el catarro, gripe, garganta, bronquios (tasa de respuesta: 99,94%)</t>
+          <t>Menores que consumieron medicamentos para  el catarro, gripe, garganta, bronquios (tasa de respuesta: 99,94%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -541,7 +541,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -654,44 +654,44 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
+          <t>52,93%</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>60,21%</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>57,19%</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
           <t>82,89%</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>48,54%</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>38,16%</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>51,87%</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>52,93%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>60,21%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>55,86%</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
           <t>66,82%</t>
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>45,66%</t>
+          <t>54,43%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>64,37; 93,88</t>
+          <t>34,05; 72,04</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>27,34; 68,53</t>
+          <t>41,21; 76,37</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>17,77; 56,08</t>
+          <t>38,11; 74,39</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -742,17 +742,17 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>33,46; 73,11</t>
+          <t>66,41; 93,52</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>41,04; 77,6</t>
+          <t>28,27; 70,37</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>36,11; 74,03</t>
+          <t>33,41; 67,01</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -762,17 +762,17 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>52,54; 79,42</t>
+          <t>51,25; 78,8</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>41,19; 67,54</t>
+          <t>40,69; 69,17</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>27,71; 59,57</t>
+          <t>42,24; 67,54</t>
         </is>
       </c>
     </row>
@@ -794,44 +794,44 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
+          <t>60,12%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>51,53%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>55,71%</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
           <t>59,16%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="I6" s="2" t="inlineStr">
         <is>
           <t>74,02%</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>67,12%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>45,96%</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>60,12%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>51,53%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>55,56%</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
           <t>59,66%</t>
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>62,11%</t>
+          <t>51,07%</t>
         </is>
       </c>
     </row>
@@ -862,17 +862,17 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>42,48; 75,63</t>
+          <t>44,4; 75,38</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>56,81; 85,38</t>
+          <t>32,47; 68,17</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>36,66; 89,47</t>
+          <t>42,34; 68,3</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -882,17 +882,17 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>43,33; 76,14</t>
+          <t>41,98; 73,99</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>31,14; 67,39</t>
+          <t>56,45; 87,36</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>42,82; 68,04</t>
+          <t>30,51; 61,23</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -902,17 +902,17 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>47,88; 69,26</t>
+          <t>47,93; 70,99</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>53,15; 76,14</t>
+          <t>53,04; 74,2</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>47,28; 81,69</t>
+          <t>42,25; 61,64</t>
         </is>
       </c>
     </row>
@@ -934,44 +934,44 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
+          <t>79,61%</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>57,59%</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>72,09%</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
           <t>70,74%</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>52,72%</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>72,14%</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>73,58%</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>79,61%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>57,59%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>72,32%</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
           <t>76,1%</t>
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>72,24%</t>
+          <t>72,82%</t>
         </is>
       </c>
     </row>
@@ -1002,17 +1002,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>49,84; 89,72</t>
+          <t>62,97; 93,17</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>23,02; 76,42</t>
+          <t>31,27; 82,92</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>53,25; 87,1</t>
+          <t>52,44; 86,36</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1022,17 +1022,17 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>59,82; 90,51</t>
+          <t>47,11; 89,62</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>31,83; 83,21</t>
+          <t>23,16; 76,42</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>54,43; 87,08</t>
+          <t>55,55; 87,28</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
@@ -1042,17 +1042,17 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>63,82; 86,51</t>
+          <t>63,1; 86,26</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>34,08; 74,94</t>
+          <t>35,26; 75,35</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>59,16; 83,99</t>
+          <t>59,91; 82,92</t>
         </is>
       </c>
     </row>
@@ -1074,44 +1074,44 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
+          <t>66,82%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>59,71%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>70,11%</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
           <t>80,35%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>55,01%</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>49,98%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>50,96%</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>66,82%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>59,71%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>72,0%</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
           <t>74,38%</t>
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>60,31%</t>
+          <t>59,77%</t>
         </is>
       </c>
     </row>
@@ -1142,17 +1142,17 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>62,1; 92,74</t>
+          <t>44,04; 82,65</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>37,93; 71,26</t>
+          <t>43,36; 76,34</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>26,27; 77,17</t>
+          <t>37,83; 90,99</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1162,17 +1162,17 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>43,65; 84,12</t>
+          <t>62,3; 91,4</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>42,24; 74,66</t>
+          <t>38,05; 71,08</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>40,51; 91,61</t>
+          <t>26,7; 76,98</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -1182,17 +1182,17 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>61,03; 84,68</t>
+          <t>60,02; 85,0</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>46,03; 68,61</t>
+          <t>46,82; 68,63</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>41,34; 77,71</t>
+          <t>38,37; 76,74</t>
         </is>
       </c>
     </row>
@@ -1214,44 +1214,44 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
+          <t>78,62%</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>72,7%</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>47,2%</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
           <t>84,25%</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="I12" s="2" t="inlineStr">
         <is>
           <t>88,16%</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>70,54%</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>70,81%</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>78,62%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>72,7%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>42,76%</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
           <t>81,67%</t>
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>54,85%</t>
+          <t>58,16%</t>
         </is>
       </c>
     </row>
@@ -1282,17 +1282,17 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>62,28; 95,54</t>
+          <t>55,26; 94,76</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>50,97; 100,0</t>
+          <t>32,67; 100,0</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>42,99; 89,06</t>
+          <t>19,48; 72,73</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1302,17 +1302,17 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>54,39; 94,74</t>
+          <t>58,45; 95,42</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>32,38; 100,0</t>
+          <t>52,6; 100,0</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>20,06; 71,27</t>
+          <t>44,36; 87,63</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -1322,17 +1322,17 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>66,37; 91,84</t>
+          <t>66,14; 91,83</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>53,67; 94,6</t>
+          <t>56,17; 95,01</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>33,53; 74,66</t>
+          <t>37,05; 75,32</t>
         </is>
       </c>
     </row>
@@ -1354,44 +1354,44 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
+          <t>57,18%</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>36,47%</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>74,21%</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
           <t>55,89%</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="I14" s="2" t="inlineStr">
         <is>
           <t>55,26%</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>60,41%</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>58,53%</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>57,18%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>36,47%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>76,04%</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
           <t>56,69%</t>
@@ -1404,7 +1404,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>70,4%</t>
+          <t>67,92%</t>
         </is>
       </c>
     </row>
@@ -1422,17 +1422,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>31,28; 81,34</t>
+          <t>36,6; 75,22</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>29,59; 83,93</t>
+          <t>9,17; 68,79</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>30,44; 84,33</t>
+          <t>50,34; 90,59</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1442,17 +1442,17 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>36,89; 75,49</t>
+          <t>30,1; 81,45</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>15,23; 72,44</t>
+          <t>23,37; 79,29</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>53,46; 89,93</t>
+          <t>28,72; 83,11</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
@@ -1462,17 +1462,17 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>42,65; 71,67</t>
+          <t>41,53; 71,93</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>26,25; 67,08</t>
+          <t>27,99; 65,1</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>53,75; 84,13</t>
+          <t>49,77; 81,16</t>
         </is>
       </c>
     </row>
@@ -1494,57 +1494,57 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
+          <t>56,26%</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>74,95%</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>55,66%</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
           <t>60,62%</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="I16" s="2" t="inlineStr">
         <is>
           <t>66,94%</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>51,52%</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>50,83%</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>56,26%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>74,95%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>58,49%</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>70,35%</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>53,64%</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>58,49%</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>70,35%</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>52,79%</t>
         </is>
       </c>
     </row>
@@ -1562,17 +1562,17 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>44,21; 75,0</t>
+          <t>39,27; 71,2</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>44,43; 85,55</t>
+          <t>49,38; 93,68</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>36,89; 66,43</t>
+          <t>37,49; 70,48</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -1582,17 +1582,17 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>39,96; 71,74</t>
+          <t>44,19; 74,97</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>48,58; 93,42</t>
+          <t>43,21; 85,1</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>37,52; 68,27</t>
+          <t>35,17; 66,71</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -1602,17 +1602,17 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>46,63; 69,0</t>
+          <t>47,7; 70,75</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>53,62; 83,72</t>
+          <t>54,49; 83,87</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>40,06; 63,18</t>
+          <t>40,38; 64,36</t>
         </is>
       </c>
     </row>
@@ -1634,44 +1634,44 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
+          <t>54,68%</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>43,22%</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>58,45%</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
           <t>52,4%</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="I18" s="2" t="inlineStr">
         <is>
           <t>56,41%</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>62,94%</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>60,8%</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>54,68%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>43,22%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>59,64%</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
           <t>53,56%</t>
@@ -1684,7 +1684,7 @@
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>60,99%</t>
+          <t>59,37%</t>
         </is>
       </c>
     </row>
@@ -1702,17 +1702,17 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>34,15; 71,3</t>
+          <t>35,64; 71,15</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>36,9; 71,64</t>
+          <t>27,59; 57,54</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>33,84; 87,34</t>
+          <t>33,45; 81,95</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -1722,17 +1722,17 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>35,14; 71,3</t>
+          <t>35,27; 69,34</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>28,67; 59,74</t>
+          <t>36,02; 71,73</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>34,02; 85,27</t>
+          <t>32,13; 88,32</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
@@ -1742,17 +1742,17 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>40,88; 66,35</t>
+          <t>41,21; 65,16</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>37,47; 60,6</t>
+          <t>37,62; 60,87</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>40,94; 77,32</t>
+          <t>39,67; 78,0</t>
         </is>
       </c>
     </row>
@@ -1774,44 +1774,44 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
+          <t>62,4%</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>55,14%</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>59,51%</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
           <t>67,23%</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="I20" s="2" t="inlineStr">
         <is>
           <t>61,36%</t>
         </is>
       </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>58,53%</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>54,53%</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>62,4%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>55,14%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>59,03%</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
           <t>64,72%</t>
@@ -1824,7 +1824,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>58,79%</t>
+          <t>57,2%</t>
         </is>
       </c>
     </row>
@@ -1842,17 +1842,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>61,17; 73,9</t>
+          <t>55,88; 68,32</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>53,74; 68,17</t>
+          <t>47,55; 62,83</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>48,28; 74,25</t>
+          <t>53,33; 66,89</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -1862,17 +1862,17 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>56,07; 69,1</t>
+          <t>60,7; 73,37</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>47,78; 62,35</t>
+          <t>53,45; 68,0</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>52,18; 65,89</t>
+          <t>47,2; 61,09</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
@@ -1882,17 +1882,17 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>59,66; 69,02</t>
+          <t>60,41; 69,13</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>52,85; 62,89</t>
+          <t>53,08; 63,13</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>53,2; 67,73</t>
+          <t>52,4; 61,93</t>
         </is>
       </c>
     </row>
@@ -1951,13 +1951,13 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que consumiero medicamentos para  el catarro, gripe, garganta, bronquios (tasa de respuesta: 99,94%)</t>
+          <t>Menores que consumieron medicamentos para  el catarro, gripe, garganta, bronquios (tasa de respuesta: 99,94%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -1965,7 +1965,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -2073,42 +2073,42 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>19</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>19</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="J4" s="2" t="inlineStr">
         <is>
           <t>18</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>17</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -2141,42 +2141,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>12135</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>9861</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>11564</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>11023</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
           <t>11668</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>13339</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="I5" s="2" t="inlineStr">
         <is>
           <t>7811</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>11595</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>12135</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>9861</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>11564</t>
-        </is>
-      </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>12469</t>
+          <t>10788</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -2196,7 +2196,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>24063</t>
+          <t>21810</t>
         </is>
       </c>
     </row>
@@ -2214,17 +2214,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>10359; 15106</t>
+          <t>6344; 13421</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>4400; 11028</t>
+          <t>7914; 14668</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>5398; 17040</t>
+          <t>7345; 14336</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -2234,17 +2234,17 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>6234; 13622</t>
+          <t>10686; 15049</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>7882; 14903</t>
+          <t>4549; 11324</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>8060; 16525</t>
+          <t>6949; 13938</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -2254,17 +2254,17 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>18245; 27578</t>
+          <t>17797; 27361</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>14539; 23839</t>
+          <t>14364; 24416</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>14604; 31395</t>
+          <t>16927; 27066</t>
         </is>
       </c>
     </row>
@@ -2281,42 +2281,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
           <t>27</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>21</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="I7" s="2" t="inlineStr">
         <is>
           <t>31</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="J7" s="2" t="inlineStr">
         <is>
           <t>25</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>41</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -2349,42 +2349,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>19856</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>15016</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>10658</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>23771</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>16730</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>13893</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>20181</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>42319</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>19856</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>15016</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>10658</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>26760</t>
+          <t>17818</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -2404,7 +2404,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>69079</t>
+          <t>41590</t>
         </is>
       </c>
     </row>
@@ -2422,17 +2422,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>9976; 17759</t>
+          <t>11088; 18827</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>15489; 23277</t>
+          <t>6716; 14099</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>23113; 56416</t>
+          <t>18064; 29144</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -2442,17 +2442,17 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>10823; 19018</t>
+          <t>9858; 17375</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>6441; 13937</t>
+          <t>15390; 23817</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>20625; 32768</t>
+          <t>11829; 23737</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
@@ -2462,17 +2462,17 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>23203; 33563</t>
+          <t>23225; 34399</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>25483; 36505</t>
+          <t>25430; 35574</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>52583; 90851</t>
+          <t>34405; 50200</t>
         </is>
       </c>
     </row>
@@ -2489,42 +2489,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>16</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="J10" s="2" t="inlineStr">
         <is>
           <t>21</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>20</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -2557,42 +2557,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>10561</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>17759</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>4802</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>12745</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
           <t>11627</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>10347</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="I11" s="2" t="inlineStr">
         <is>
           <t>5020</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>12943</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>10561</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>17759</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>4802</t>
-        </is>
-      </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>14671</t>
+          <t>12655</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2612,7 +2612,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>27614</t>
+          <t>25400</t>
         </is>
       </c>
     </row>
@@ -2630,17 +2630,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>7290; 13123</t>
+          <t>14047; 20786</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>2192; 7277</t>
+          <t>2608; 6914</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>9554; 15627</t>
+          <t>9272; 15268</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -2650,17 +2650,17 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>13345; 20192</t>
+          <t>6891; 13109</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>2654; 6939</t>
+          <t>2206; 7278</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>11042; 17666</t>
+          <t>9555; 15011</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -2670,17 +2670,17 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>23574; 31954</t>
+          <t>23308; 31861</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>6088; 13386</t>
+          <t>6299; 13459</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>22614; 32106</t>
+          <t>20895; 28921</t>
         </is>
       </c>
     </row>
@@ -2697,37 +2697,37 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
           <t>24</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t>22</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="I13" s="2" t="inlineStr">
         <is>
           <t>20</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>21</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -2765,42 +2765,42 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>16426</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>10184</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>15273</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>7302</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
           <t>16351</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>15523</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="I14" s="2" t="inlineStr">
         <is>
           <t>13092</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>6258</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>16426</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>10184</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>15273</t>
-        </is>
-      </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>7973</t>
+          <t>6229</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2820,7 +2820,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>14230</t>
+          <t>13531</t>
         </is>
       </c>
     </row>
@@ -2838,17 +2838,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>11997; 17916</t>
+          <t>6712; 12597</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>9028; 16960</t>
+          <t>11092; 19528</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>3289; 9663</t>
+          <t>3941; 9477</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2858,17 +2858,17 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>6653; 12822</t>
+          <t>12036; 17657</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>10805; 19098</t>
+          <t>9055; 16917</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>4486; 10144</t>
+          <t>3264; 9409</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
@@ -2878,17 +2878,17 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>21093; 29268</t>
+          <t>20744; 29375</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>22730; 33880</t>
+          <t>23118; 33888</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>9754; 18335</t>
+          <t>8688; 17372</t>
         </is>
       </c>
     </row>
@@ -2905,42 +2905,42 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
           <t>13</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="I16" s="2" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
+      <c r="J16" s="2" t="inlineStr">
         <is>
           <t>11</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -2973,42 +2973,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>7820</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>9660</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>3757</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>4598</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
           <t>9126</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="H17" s="2" t="inlineStr">
         <is>
           <t>12223</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="I17" s="2" t="inlineStr">
         <is>
           <t>5740</t>
         </is>
       </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>5810</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>7820</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>9660</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>3757</t>
-        </is>
-      </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>4570</t>
+          <t>5976</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -3028,7 +3028,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>10381</t>
+          <t>10574</t>
         </is>
       </c>
     </row>
@@ -3046,17 +3046,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>9035; 13861</t>
+          <t>6790; 11643</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>3319; 6511</t>
+          <t>1688; 5168</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>3541; 7336</t>
+          <t>1898; 7084</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -3066,17 +3066,17 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>6683; 11641</t>
+          <t>8480; 13843</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>1673; 5168</t>
+          <t>3425; 6511</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>2144; 7618</t>
+          <t>3744; 7396</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -3086,17 +3086,17 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>17783; 24609</t>
+          <t>17722; 24606</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>6268; 11048</t>
+          <t>6560; 11097</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>6347; 14130</t>
+          <t>6736; 13693</t>
         </is>
       </c>
     </row>
@@ -3113,42 +3113,42 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
           <t>18</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="H19" s="2" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
+      <c r="I19" s="2" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
+      <c r="J19" s="2" t="inlineStr">
         <is>
           <t>8</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>17</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
@@ -3181,42 +3181,42 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>10729</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>10346</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>3167</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>8488</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
           <t>12379</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="H20" s="2" t="inlineStr">
         <is>
           <t>6141</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="I20" s="2" t="inlineStr">
         <is>
           <t>5031</t>
         </is>
       </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>4639</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>10729</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>10346</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>3167</t>
-        </is>
-      </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>10347</t>
+          <t>4485</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>14987</t>
+          <t>12972</t>
         </is>
       </c>
     </row>
@@ -3254,17 +3254,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>3437; 8938</t>
+          <t>6622; 13610</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>2694; 7642</t>
+          <t>797; 5974</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>2338; 6476</t>
+          <t>5758; 10362</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -3274,17 +3274,17 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>6674; 13658</t>
+          <t>3308; 8950</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>1323; 6291</t>
+          <t>2128; 7219</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>7275; 12237</t>
+          <t>2201; 6368</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
@@ -3294,17 +3294,17 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>12404; 20841</t>
+          <t>12077; 20919</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>4670; 11933</t>
+          <t>4980; 11581</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>11442; 17908</t>
+          <t>9505; 15500</t>
         </is>
       </c>
     </row>
@@ -3321,42 +3321,42 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
           <t>31</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
         <is>
           <t>23</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
+      <c r="I22" s="2" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="F22" s="2" t="inlineStr">
+      <c r="J22" s="2" t="inlineStr">
         <is>
           <t>23</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>38</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>31</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
@@ -3389,42 +3389,42 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>26526</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>14259</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>7947</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>23394</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
           <t>21499</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="H23" s="2" t="inlineStr">
         <is>
           <t>16099</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
+      <c r="I23" s="2" t="inlineStr">
         <is>
           <t>9539</t>
         </is>
       </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>15347</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>26526</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>14259</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>7947</t>
-        </is>
-      </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>23789</t>
+          <t>15386</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3444,7 +3444,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>39136</t>
+          <t>38779</t>
         </is>
       </c>
     </row>
@@ -3462,17 +3462,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>11741; 19918</t>
+          <t>9952; 18045</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>6331; 12191</t>
+          <t>5236; 9934</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>10988; 19786</t>
+          <t>15756; 29623</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3482,17 +3482,17 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>10128; 18183</t>
+          <t>11738; 19912</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>5152; 9906</t>
+          <t>6158; 12127</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>16640; 30282</t>
+          <t>10644; 20192</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
@@ -3502,17 +3502,17 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>24201; 35814</t>
+          <t>24761; 36720</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>13326; 20807</t>
+          <t>13543; 20846</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>29701; 46845</t>
+          <t>29194; 46529</t>
         </is>
       </c>
     </row>
@@ -3529,42 +3529,42 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
           <t>42</t>
         </is>
       </c>
-      <c r="D25" s="2" t="inlineStr">
+      <c r="H25" s="2" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="E25" s="2" t="inlineStr">
+      <c r="I25" s="2" t="inlineStr">
         <is>
           <t>19</t>
         </is>
       </c>
-      <c r="F25" s="2" t="inlineStr">
+      <c r="J25" s="2" t="inlineStr">
         <is>
           <t>9</t>
-        </is>
-      </c>
-      <c r="G25" s="2" t="inlineStr">
-        <is>
-          <t>62</t>
-        </is>
-      </c>
-      <c r="H25" s="2" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="I25" s="2" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="J25" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
@@ -3597,42 +3597,42 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
+          <t>39867</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>11862</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>10811</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>6842</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
           <t>25924</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
+      <c r="H26" s="2" t="inlineStr">
         <is>
           <t>11121</t>
         </is>
       </c>
-      <c r="E26" s="2" t="inlineStr">
+      <c r="I26" s="2" t="inlineStr">
         <is>
           <t>11800</t>
         </is>
       </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>5106</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
-        <is>
-          <t>39867</t>
-        </is>
-      </c>
-      <c r="H26" s="2" t="inlineStr">
-        <is>
-          <t>11862</t>
-        </is>
-      </c>
-      <c r="I26" s="2" t="inlineStr">
-        <is>
-          <t>10811</t>
-        </is>
-      </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>6982</t>
+          <t>4641</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
@@ -3652,7 +3652,7 @@
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>12088</t>
+          <t>11484</t>
         </is>
       </c>
     </row>
@@ -3670,17 +3670,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>7248; 15133</t>
+          <t>7730; 15433</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>7718; 14986</t>
+          <t>6902; 14393</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>2745; 7086</t>
+          <t>3916; 9594</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3690,17 +3690,17 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>7622; 15467</t>
+          <t>7485; 14715</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>7172; 14942</t>
+          <t>7535; 15005</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>3983; 9983</t>
+          <t>2453; 6742</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
@@ -3710,17 +3710,17 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>17545; 28472</t>
+          <t>17683; 27964</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>17211; 27833</t>
+          <t>17278; 27960</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>8115; 15324</t>
+          <t>7673; 15086</t>
         </is>
       </c>
     </row>
@@ -3737,42 +3737,42 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
+          <t>215</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>138</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>155</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
           <t>190</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
+      <c r="H28" s="2" t="inlineStr">
         <is>
           <t>141</t>
         </is>
       </c>
-      <c r="E28" s="2" t="inlineStr">
+      <c r="I28" s="2" t="inlineStr">
         <is>
           <t>119</t>
         </is>
       </c>
-      <c r="F28" s="2" t="inlineStr">
+      <c r="J28" s="2" t="inlineStr">
         <is>
           <t>125</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr">
-        <is>
-          <t>215</t>
-        </is>
-      </c>
-      <c r="H28" s="2" t="inlineStr">
-        <is>
-          <t>138</t>
-        </is>
-      </c>
-      <c r="I28" s="2" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J28" s="2" t="inlineStr">
-        <is>
-          <t>155</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr">
@@ -3805,42 +3805,42 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
+          <t>143919</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>98947</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>67979</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>98162</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
           <t>125305</t>
         </is>
       </c>
-      <c r="D29" s="2" t="inlineStr">
+      <c r="H29" s="2" t="inlineStr">
         <is>
           <t>98686</t>
         </is>
       </c>
-      <c r="E29" s="2" t="inlineStr">
+      <c r="I29" s="2" t="inlineStr">
         <is>
           <t>78212</t>
         </is>
       </c>
-      <c r="F29" s="2" t="inlineStr">
-        <is>
-          <t>104018</t>
-        </is>
-      </c>
-      <c r="G29" s="2" t="inlineStr">
-        <is>
-          <t>143919</t>
-        </is>
-      </c>
-      <c r="H29" s="2" t="inlineStr">
-        <is>
-          <t>98947</t>
-        </is>
-      </c>
-      <c r="I29" s="2" t="inlineStr">
-        <is>
-          <t>67979</t>
-        </is>
-      </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>107562</t>
+          <t>77978</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
@@ -3860,7 +3860,7 @@
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>211579</t>
+          <t>176140</t>
         </is>
       </c>
     </row>
@@ -3878,17 +3878,17 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>89801; 108483</t>
+          <t>88618; 108340</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>68501; 86885</t>
+          <t>58624; 77455</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>85806; 131950</t>
+          <t>87974; 110339</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3898,17 +3898,17 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>88910; 109578</t>
+          <t>89108; 107709</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>58903; 76857</t>
+          <t>68124; 86669</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>95069; 120047</t>
+          <t>67490; 87349</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
@@ -3918,17 +3918,17 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>182190; 210777</t>
+          <t>184488; 211108</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>132523; 157678</t>
+          <t>133087; 158295</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>191488; 243782</t>
+          <t>161358; 190697</t>
         </is>
       </c>
     </row>
